--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
   <si>
     <t>No.</t>
   </si>
@@ -35,25 +35,43 @@
     <t>평균</t>
   </si>
   <si>
-    <t>464.3</t>
+    <t>475.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.6</t>
+    <t>4.8</t>
   </si>
   <si>
     <t>01일</t>
   </si>
   <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
     <t>02일</t>
   </si>
   <si>
+    <t>485.4</t>
+  </si>
+  <si>
+    <t>950.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>03일</t>
   </si>
   <si>
     <t>04일</t>
@@ -448,16 +466,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s" s="31">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s" s="32">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s" s="33">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s" s="34">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -465,19 +483,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s" s="35">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s" s="36">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="37">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -485,19 +503,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -505,19 +523,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -525,19 +543,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -545,19 +563,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -565,19 +583,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -585,19 +603,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -605,19 +623,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -625,19 +643,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -645,19 +663,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -665,19 +683,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -685,19 +703,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -705,19 +723,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -725,19 +743,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -745,19 +763,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -765,19 +783,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -785,19 +803,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -805,19 +823,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -825,19 +843,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -845,19 +863,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -865,19 +883,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -885,19 +903,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -905,19 +923,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -925,19 +943,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -945,19 +963,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -965,19 +983,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -985,19 +1003,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1005,19 +1023,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1025,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1045,19 +1063,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>475.4</t>
+    <t>501.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>5.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -56,10 +56,10 @@
     <t>02일</t>
   </si>
   <si>
-    <t>485.4</t>
-  </si>
-  <si>
-    <t>950.9</t>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
   </si>
   <si>
     <t>4.9</t>
@@ -71,10 +71,22 @@
     <t>03일</t>
   </si>
   <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>04일</t>
   </si>
   <si>
     <t>05일</t>
@@ -509,13 +521,13 @@
         <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -523,19 +535,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -543,19 +555,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -563,19 +575,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -583,19 +595,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -603,19 +615,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -623,19 +635,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -643,19 +655,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -663,19 +675,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -723,19 +735,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -743,19 +755,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -763,19 +775,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -783,19 +795,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -803,19 +815,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -823,19 +835,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -843,19 +855,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>501.4</t>
+    <t>512.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.0</t>
+    <t>5.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -86,10 +86,22 @@
     <t>04일</t>
   </si>
   <si>
+    <t>544.9</t>
+  </si>
+  <si>
+    <t>2049.0</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>05일</t>
   </si>
   <si>
     <t>06일</t>
@@ -541,13 +553,13 @@
         <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -555,19 +567,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -575,19 +587,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -595,19 +607,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -615,19 +627,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -635,19 +647,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -655,19 +667,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -675,19 +687,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -695,19 +707,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -715,19 +727,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -735,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -755,19 +767,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -775,19 +787,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -795,19 +807,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -815,19 +827,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -835,19 +847,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -855,19 +867,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -875,19 +887,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -895,19 +907,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -915,19 +927,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -935,19 +947,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -955,19 +967,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -975,19 +987,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -995,19 +1007,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1015,19 +1027,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1035,19 +1047,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1055,19 +1067,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1075,19 +1087,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="59">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>512.3</t>
+    <t>509.8</t>
   </si>
   <si>
     <t>-</t>
@@ -86,13 +86,10 @@
     <t>04일</t>
   </si>
   <si>
-    <t>544.9</t>
-  </si>
-  <si>
-    <t>2049.0</t>
-  </si>
-  <si>
-    <t>5.4</t>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
   </si>
   <si>
     <t>20.5</t>
@@ -101,10 +98,22 @@
     <t>05일</t>
   </si>
   <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>06일</t>
   </si>
   <si>
     <t>07일</t>
@@ -556,10 +565,10 @@
         <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s" s="39">
         <v>26</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>27</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -567,19 +576,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>28</v>
-      </c>
-      <c r="C7" t="s" s="31">
-        <v>29</v>
       </c>
       <c r="D7" t="s" s="32">
         <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -587,19 +596,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -607,19 +616,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -627,19 +636,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -647,19 +656,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -667,19 +676,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -687,19 +696,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -707,19 +716,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -727,19 +736,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -747,19 +756,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -767,19 +776,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -787,19 +796,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -807,19 +816,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -827,19 +836,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -847,19 +856,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -867,19 +876,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -887,19 +896,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -907,19 +916,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -927,19 +936,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -947,19 +956,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -967,19 +976,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -987,19 +996,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1007,19 +1016,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1027,19 +1036,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1047,19 +1056,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1067,19 +1076,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1087,19 +1096,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>509.8</t>
+    <t>518.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>5.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -113,10 +113,22 @@
     <t>06일</t>
   </si>
   <si>
+    <t>559.1</t>
+  </si>
+  <si>
+    <t>3108.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>07일</t>
   </si>
   <si>
     <t>08일</t>
@@ -602,13 +614,13 @@
         <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -616,19 +628,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -636,19 +648,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -656,19 +668,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -676,19 +688,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -696,19 +708,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -716,19 +728,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -736,19 +748,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -756,19 +768,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -776,19 +788,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -796,19 +808,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -816,19 +828,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -836,19 +848,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -856,19 +868,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -876,19 +888,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -896,19 +908,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -916,19 +928,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -936,19 +948,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -956,19 +968,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -976,19 +988,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -996,19 +1008,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1016,19 +1028,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1036,19 +1048,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1056,19 +1068,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1076,19 +1088,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1096,19 +1108,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="66">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>518.0</t>
+    <t>518.7</t>
   </si>
   <si>
     <t>-</t>
@@ -128,10 +128,19 @@
     <t>07일</t>
   </si>
   <si>
+    <t>522.6</t>
+  </si>
+  <si>
+    <t>3630.9</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>08일</t>
   </si>
   <si>
     <t>09일</t>
@@ -634,13 +643,13 @@
         <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -648,19 +657,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -668,19 +677,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -688,19 +697,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -708,19 +717,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -728,19 +737,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -748,19 +757,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -768,19 +777,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -788,19 +797,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -808,19 +817,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -828,19 +837,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -848,19 +857,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -868,19 +877,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -888,19 +897,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -908,19 +917,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -928,19 +937,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -948,19 +957,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -968,19 +977,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -988,19 +997,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1008,19 +1017,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1028,19 +1037,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1048,19 +1057,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1068,19 +1077,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1088,19 +1097,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1108,19 +1117,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>518.7</t>
+    <t>513.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.2</t>
+    <t>5.1</t>
   </si>
   <si>
     <t>01일</t>
@@ -128,22 +128,34 @@
     <t>07일</t>
   </si>
   <si>
-    <t>522.6</t>
-  </si>
-  <si>
-    <t>3630.9</t>
-  </si>
-  <si>
-    <t>36.3</t>
+    <t>530.7</t>
+  </si>
+  <si>
+    <t>3639.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
   </si>
   <si>
     <t>08일</t>
   </si>
   <si>
+    <t>472.4</t>
+  </si>
+  <si>
+    <t>4111.4</t>
+  </si>
+  <si>
+    <t>41.1</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>09일</t>
   </si>
   <si>
     <t>10일</t>
@@ -646,10 +658,10 @@
         <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -657,19 +669,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -677,19 +689,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -697,19 +709,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -717,19 +729,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -737,19 +749,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -757,19 +769,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -777,19 +789,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -797,19 +809,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -817,19 +829,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -837,19 +849,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -857,19 +869,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -877,19 +889,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -897,19 +909,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -917,19 +929,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -937,19 +949,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -957,19 +969,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -977,19 +989,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -997,19 +1009,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1017,19 +1029,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1037,19 +1049,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1057,19 +1069,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1077,19 +1089,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1097,19 +1109,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1117,19 +1129,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="74">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>513.9</t>
+    <t>500.8</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>5.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -104,9 +104,6 @@
     <t>2549.2</t>
   </si>
   <si>
-    <t>5.0</t>
-  </si>
-  <si>
     <t>25.5</t>
   </si>
   <si>
@@ -143,22 +140,37 @@
     <t>08일</t>
   </si>
   <si>
-    <t>472.4</t>
-  </si>
-  <si>
-    <t>4111.4</t>
-  </si>
-  <si>
-    <t>41.1</t>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>4122.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>41.2</t>
   </si>
   <si>
     <t>09일</t>
   </si>
   <si>
+    <t>384.3</t>
+  </si>
+  <si>
+    <t>4506.9</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>45.1</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>10일</t>
   </si>
   <si>
     <t>11일</t>
@@ -618,10 +630,10 @@
         <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s" s="34">
         <v>30</v>
-      </c>
-      <c r="F7" t="s" s="34">
-        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -629,19 +641,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s" s="36">
         <v>32</v>
       </c>
-      <c r="C8" t="s" s="36">
+      <c r="D8" t="s" s="37">
         <v>33</v>
       </c>
-      <c r="D8" t="s" s="37">
+      <c r="E8" t="s" s="38">
         <v>34</v>
       </c>
-      <c r="E8" t="s" s="38">
+      <c r="F8" t="s" s="39">
         <v>35</v>
-      </c>
-      <c r="F8" t="s" s="39">
-        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -649,19 +661,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s" s="31">
         <v>37</v>
       </c>
-      <c r="C9" t="s" s="31">
+      <c r="D9" t="s" s="32">
         <v>38</v>
       </c>
-      <c r="D9" t="s" s="32">
+      <c r="E9" t="s" s="33">
         <v>39</v>
       </c>
-      <c r="E9" t="s" s="33">
+      <c r="F9" t="s" s="34">
         <v>40</v>
-      </c>
-      <c r="F9" t="s" s="34">
-        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -669,16 +681,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s" s="36">
         <v>42</v>
       </c>
-      <c r="C10" t="s" s="36">
+      <c r="D10" t="s" s="37">
         <v>43</v>
       </c>
-      <c r="D10" t="s" s="37">
+      <c r="E10" t="s" s="38">
         <v>44</v>
-      </c>
-      <c r="E10" t="s" s="38">
-        <v>12</v>
       </c>
       <c r="F10" t="s" s="39">
         <v>45</v>
@@ -695,13 +707,13 @@
         <v>47</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -709,19 +721,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -729,19 +741,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -749,19 +761,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -769,19 +781,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -789,19 +801,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -809,19 +821,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -829,19 +841,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -849,19 +861,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -869,19 +881,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -889,19 +901,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -909,19 +921,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -929,19 +941,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -949,19 +961,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -969,19 +981,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -989,19 +1001,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1009,19 +1021,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1029,19 +1041,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1049,19 +1061,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1069,19 +1081,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1089,19 +1101,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1109,19 +1121,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1129,19 +1141,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="78">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>500.8</t>
+    <t>497.3</t>
   </si>
   <si>
     <t>-</t>
@@ -155,25 +155,37 @@
     <t>09일</t>
   </si>
   <si>
-    <t>384.3</t>
-  </si>
-  <si>
-    <t>4506.9</t>
-  </si>
-  <si>
-    <t>3.8</t>
-  </si>
-  <si>
-    <t>45.1</t>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>4517.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>45.2</t>
   </si>
   <si>
     <t>10일</t>
   </si>
   <si>
+    <t>456.2</t>
+  </si>
+  <si>
+    <t>4973.4</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>49.7</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>11일</t>
   </si>
   <si>
     <t>12일</t>
@@ -727,13 +739,13 @@
         <v>52</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -741,19 +753,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -761,19 +773,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -781,19 +793,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -801,19 +813,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -821,19 +833,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -841,19 +853,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -861,19 +873,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -881,19 +893,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -901,19 +913,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -921,19 +933,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -941,19 +953,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -961,19 +973,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -981,19 +993,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1001,19 +1013,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1021,19 +1033,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1041,19 +1053,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1061,19 +1073,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1081,19 +1093,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1101,19 +1113,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1121,19 +1133,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1141,19 +1153,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="81">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>497.3</t>
+    <t>495.6</t>
   </si>
   <si>
     <t>-</t>
@@ -170,25 +170,34 @@
     <t>10일</t>
   </si>
   <si>
-    <t>456.2</t>
-  </si>
-  <si>
-    <t>4973.4</t>
+    <t>460.2</t>
+  </si>
+  <si>
+    <t>4977.4</t>
   </si>
   <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>49.7</t>
+    <t>49.8</t>
   </si>
   <si>
     <t>11일</t>
   </si>
   <si>
+    <t>474.5</t>
+  </si>
+  <si>
+    <t>5451.9</t>
+  </si>
+  <si>
+    <t>54.5</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>12일</t>
   </si>
   <si>
     <t>13일</t>
@@ -759,13 +768,13 @@
         <v>57</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -773,19 +782,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -793,19 +802,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -813,19 +822,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -833,19 +842,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -853,19 +862,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -873,19 +882,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -893,19 +902,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -913,19 +922,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -933,19 +942,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -953,19 +962,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -973,19 +982,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -993,19 +1002,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1013,19 +1022,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1033,19 +1042,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1053,19 +1062,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1073,19 +1082,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1093,19 +1102,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1113,19 +1122,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1133,19 +1142,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1153,19 +1162,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>495.6</t>
+    <t>501.1</t>
   </si>
   <si>
     <t>-</t>
@@ -185,22 +185,31 @@
     <t>11일</t>
   </si>
   <si>
-    <t>474.5</t>
-  </si>
-  <si>
-    <t>5451.9</t>
-  </si>
-  <si>
-    <t>54.5</t>
+    <t>480.9</t>
+  </si>
+  <si>
+    <t>5458.3</t>
+  </si>
+  <si>
+    <t>54.6</t>
   </si>
   <si>
     <t>12일</t>
   </si>
   <si>
+    <t>554.9</t>
+  </si>
+  <si>
+    <t>6013.2</t>
+  </si>
+  <si>
+    <t>60.1</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>13일</t>
   </si>
   <si>
     <t>14일</t>
@@ -771,7 +780,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>59</v>
@@ -788,13 +797,13 @@
         <v>61</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -802,19 +811,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -822,19 +831,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -842,19 +851,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -862,19 +871,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -882,19 +891,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -902,19 +911,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -922,19 +931,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -942,19 +951,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -962,19 +971,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -982,19 +991,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1002,19 +1011,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1022,19 +1031,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1042,19 +1051,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1062,19 +1071,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1082,19 +1091,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1102,19 +1111,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1122,19 +1131,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1142,19 +1151,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1162,19 +1171,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
   <si>
     <t>No.</t>
   </si>
@@ -35,75 +35,75 @@
     <t>평균</t>
   </si>
   <si>
-    <t>501.1</t>
+    <t>490.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
     <t>5.0</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>552.2</t>
-  </si>
-  <si>
-    <t>1504.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>545.0</t>
-  </si>
-  <si>
-    <t>2049.1</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>500.1</t>
-  </si>
-  <si>
-    <t>2549.2</t>
-  </si>
-  <si>
     <t>25.5</t>
   </si>
   <si>
@@ -197,22 +197,34 @@
     <t>12일</t>
   </si>
   <si>
-    <t>554.9</t>
-  </si>
-  <si>
-    <t>6013.2</t>
-  </si>
-  <si>
-    <t>60.1</t>
+    <t>559.0</t>
+  </si>
+  <si>
+    <t>6017.3</t>
+  </si>
+  <si>
+    <t>60.2</t>
   </si>
   <si>
     <t>13일</t>
   </si>
   <si>
+    <t>364.1</t>
+  </si>
+  <si>
+    <t>6381.4</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>63.8</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>14일</t>
   </si>
   <si>
     <t>15일</t>
@@ -600,10 +612,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s" s="39">
         <v>16</v>
-      </c>
-      <c r="F4" t="s" s="39">
-        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -611,19 +623,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s" s="31">
         <v>18</v>
       </c>
-      <c r="C5" t="s" s="31">
+      <c r="D5" t="s" s="32">
         <v>19</v>
       </c>
-      <c r="D5" t="s" s="32">
+      <c r="E5" t="s" s="33">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="33">
+      <c r="F5" t="s" s="34">
         <v>21</v>
-      </c>
-      <c r="F5" t="s" s="34">
-        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -631,19 +643,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s" s="36">
         <v>23</v>
       </c>
-      <c r="C6" t="s" s="36">
+      <c r="D6" t="s" s="37">
         <v>24</v>
       </c>
-      <c r="D6" t="s" s="37">
+      <c r="E6" t="s" s="38">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s" s="39">
         <v>25</v>
-      </c>
-      <c r="E6" t="s" s="38">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s" s="39">
-        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -651,16 +663,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="31">
         <v>27</v>
       </c>
-      <c r="C7" t="s" s="31">
+      <c r="D7" t="s" s="32">
         <v>28</v>
       </c>
-      <c r="D7" t="s" s="32">
+      <c r="E7" t="s" s="33">
         <v>29</v>
-      </c>
-      <c r="E7" t="s" s="33">
-        <v>9</v>
       </c>
       <c r="F7" t="s" s="34">
         <v>30</v>
@@ -800,7 +812,7 @@
         <v>62</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s" s="39">
         <v>63</v>
@@ -817,13 +829,13 @@
         <v>65</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -831,19 +843,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -851,19 +863,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -871,19 +883,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -891,19 +903,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -911,19 +923,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -931,19 +943,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -951,19 +963,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -971,19 +983,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -991,19 +1003,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1011,19 +1023,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1031,19 +1043,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1051,19 +1063,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1071,19 +1083,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1091,19 +1103,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1111,19 +1123,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1131,19 +1143,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1151,19 +1163,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1171,19 +1183,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>No.</t>
   </si>
@@ -35,33 +35,36 @@
     <t>평균</t>
   </si>
   <si>
-    <t>490.9</t>
+    <t>480.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
     <t>4.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
     <t>9.5</t>
   </si>
   <si>
@@ -146,9 +149,6 @@
     <t>4122.6</t>
   </si>
   <si>
-    <t>4.8</t>
-  </si>
-  <si>
     <t>41.2</t>
   </si>
   <si>
@@ -209,25 +209,37 @@
     <t>13일</t>
   </si>
   <si>
-    <t>364.1</t>
-  </si>
-  <si>
-    <t>6381.4</t>
-  </si>
-  <si>
-    <t>3.6</t>
-  </si>
-  <si>
-    <t>63.8</t>
+    <t>368.3</t>
+  </si>
+  <si>
+    <t>6385.6</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>63.9</t>
   </si>
   <si>
     <t>14일</t>
   </si>
   <si>
+    <t>334.5</t>
+  </si>
+  <si>
+    <t>6720.1</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>67.2</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>15일</t>
   </si>
   <si>
     <t>16일</t>
@@ -612,10 +624,10 @@
         <v>15</v>
       </c>
       <c r="E4" t="s" s="38">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="39">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1">
@@ -623,19 +635,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s" s="30">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s" s="31">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="32">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="33">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s" s="34">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="17.25" customHeight="1">
@@ -643,19 +655,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s" s="35">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s" s="36">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s" s="37">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s" s="38">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s" s="39">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -663,19 +675,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s" s="30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s" s="31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s" s="32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="34">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1">
@@ -683,19 +695,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s" s="35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s" s="37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s" s="38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="39">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="17.25" customHeight="1">
@@ -703,19 +715,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s" s="30">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s" s="31">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s" s="32">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s" s="33">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s" s="34">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1">
@@ -723,16 +735,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s" s="35">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s" s="36">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s" s="37">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s" s="39">
         <v>45</v>
@@ -792,7 +804,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>59</v>
@@ -812,7 +824,7 @@
         <v>62</v>
       </c>
       <c r="E14" t="s" s="38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s" s="39">
         <v>63</v>
@@ -849,13 +861,13 @@
         <v>70</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -863,19 +875,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -883,19 +895,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -903,19 +915,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -923,19 +935,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -943,19 +955,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -963,19 +975,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -983,19 +995,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1003,19 +1015,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1023,19 +1035,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1043,19 +1055,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1063,19 +1075,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1083,19 +1095,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1103,19 +1115,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1123,19 +1135,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1143,19 +1155,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1163,19 +1175,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1183,19 +1195,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="96">
   <si>
     <t>No.</t>
   </si>
@@ -35,120 +35,123 @@
     <t>평균</t>
   </si>
   <si>
-    <t>480.0</t>
+    <t>461.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>559.1</t>
+  </si>
+  <si>
+    <t>3108.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>530.7</t>
+  </si>
+  <si>
+    <t>3639.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>4122.6</t>
+  </si>
+  <si>
     <t>4.8</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>552.2</t>
-  </si>
-  <si>
-    <t>1504.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>545.0</t>
-  </si>
-  <si>
-    <t>2049.1</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>500.1</t>
-  </si>
-  <si>
-    <t>2549.2</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>559.1</t>
-  </si>
-  <si>
-    <t>3108.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>31.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>530.7</t>
-  </si>
-  <si>
-    <t>3639.0</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>36.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>483.6</t>
-  </si>
-  <si>
-    <t>4122.6</t>
-  </si>
-  <si>
     <t>41.2</t>
   </si>
   <si>
@@ -176,9 +179,6 @@
     <t>4977.4</t>
   </si>
   <si>
-    <t>4.6</t>
-  </si>
-  <si>
     <t>49.8</t>
   </si>
   <si>
@@ -224,13 +224,13 @@
     <t>14일</t>
   </si>
   <si>
-    <t>334.5</t>
-  </si>
-  <si>
-    <t>6720.1</t>
-  </si>
-  <si>
-    <t>3.3</t>
+    <t>337.8</t>
+  </si>
+  <si>
+    <t>6723.4</t>
+  </si>
+  <si>
+    <t>3.4</t>
   </si>
   <si>
     <t>67.2</t>
@@ -239,10 +239,22 @@
     <t>15일</t>
   </si>
   <si>
+    <t>199.7</t>
+  </si>
+  <si>
+    <t>6923.1</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>69.2</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>16일</t>
   </si>
   <si>
     <t>17일</t>
@@ -744,10 +756,10 @@
         <v>44</v>
       </c>
       <c r="E10" t="s" s="38">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s" s="39">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="17.25" customHeight="1">
@@ -755,19 +767,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s" s="30">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s" s="32">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -775,16 +787,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s" s="39">
         <v>55</v>
@@ -804,7 +816,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="s" s="33">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s" s="34">
         <v>59</v>
@@ -881,13 +893,13 @@
         <v>75</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -895,19 +907,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -915,19 +927,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -935,19 +947,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -955,19 +967,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -975,19 +987,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -995,19 +1007,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1015,19 +1027,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1035,19 +1047,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1055,19 +1067,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1075,19 +1087,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1095,19 +1107,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1115,19 +1127,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1135,19 +1147,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1155,19 +1167,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1175,19 +1187,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1195,19 +1207,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="101">
   <si>
     <t>No.</t>
   </si>
@@ -35,150 +35,153 @@
     <t>평균</t>
   </si>
   <si>
-    <t>461.5</t>
+    <t>441.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>559.1</t>
+  </si>
+  <si>
+    <t>3108.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>530.7</t>
+  </si>
+  <si>
+    <t>3639.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>4122.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>4517.2</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>460.2</t>
+  </si>
+  <si>
+    <t>4977.4</t>
+  </si>
+  <si>
     <t>4.6</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>552.2</t>
-  </si>
-  <si>
-    <t>1504.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>545.0</t>
-  </si>
-  <si>
-    <t>2049.1</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>500.1</t>
-  </si>
-  <si>
-    <t>2549.2</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>559.1</t>
-  </si>
-  <si>
-    <t>3108.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>31.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>530.7</t>
-  </si>
-  <si>
-    <t>3639.0</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>36.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>483.6</t>
-  </si>
-  <si>
-    <t>4122.6</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>41.2</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>4517.2</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>460.2</t>
-  </si>
-  <si>
-    <t>4977.4</t>
-  </si>
-  <si>
     <t>49.8</t>
   </si>
   <si>
@@ -239,25 +242,37 @@
     <t>15일</t>
   </si>
   <si>
-    <t>199.7</t>
-  </si>
-  <si>
-    <t>6923.1</t>
-  </si>
-  <si>
-    <t>2.0</t>
-  </si>
-  <si>
-    <t>69.2</t>
+    <t>210.0</t>
+  </si>
+  <si>
+    <t>6933.4</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>69.3</t>
   </si>
   <si>
     <t>16일</t>
   </si>
   <si>
+    <t>134.0</t>
+  </si>
+  <si>
+    <t>7067.4</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>70.7</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>17일</t>
   </si>
   <si>
     <t>18일</t>
@@ -796,10 +811,10 @@
         <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -807,19 +822,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>45</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -827,19 +842,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
         <v>35</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -847,19 +862,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -867,19 +882,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -887,19 +902,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -907,19 +922,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -927,19 +942,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -947,19 +962,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -967,19 +982,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -987,19 +1002,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1007,19 +1022,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1027,19 +1042,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1047,19 +1062,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1067,19 +1082,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1087,19 +1102,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1107,19 +1122,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1127,19 +1142,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1147,19 +1162,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1167,19 +1182,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1187,19 +1202,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1207,19 +1222,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="105">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>441.7</t>
+    <t>425.9</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.4</t>
+    <t>4.3</t>
   </si>
   <si>
     <t>01일</t>
@@ -257,25 +257,37 @@
     <t>16일</t>
   </si>
   <si>
-    <t>134.0</t>
-  </si>
-  <si>
-    <t>7067.4</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>70.7</t>
+    <t>148.3</t>
+  </si>
+  <si>
+    <t>7081.7</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>70.8</t>
   </si>
   <si>
     <t>17일</t>
   </si>
   <si>
+    <t>158.7</t>
+  </si>
+  <si>
+    <t>7240.4</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>72.4</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>18일</t>
   </si>
   <si>
     <t>19일</t>
@@ -948,13 +960,13 @@
         <v>86</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -962,19 +974,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -982,19 +994,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1002,19 +1014,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1022,19 +1034,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1042,19 +1054,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1062,19 +1074,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1082,19 +1094,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1102,19 +1114,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1122,19 +1134,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1142,19 +1154,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1162,19 +1174,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1182,19 +1194,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1202,19 +1214,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1222,19 +1234,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>425.9</t>
+    <t>430.8</t>
   </si>
   <si>
     <t>-</t>
@@ -272,10 +272,10 @@
     <t>17일</t>
   </si>
   <si>
-    <t>158.7</t>
-  </si>
-  <si>
-    <t>7240.4</t>
+    <t>160.9</t>
+  </si>
+  <si>
+    <t>7242.6</t>
   </si>
   <si>
     <t>1.6</t>
@@ -287,10 +287,22 @@
     <t>18일</t>
   </si>
   <si>
+    <t>511.7</t>
+  </si>
+  <si>
+    <t>7754.3</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>77.5</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>19일</t>
   </si>
   <si>
     <t>20일</t>
@@ -980,13 +992,13 @@
         <v>91</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -994,19 +1006,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1014,19 +1026,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1034,19 +1046,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1054,19 +1066,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1074,19 +1086,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1094,19 +1106,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1114,19 +1126,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1134,19 +1146,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1154,19 +1166,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1174,19 +1186,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1194,19 +1206,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1214,19 +1226,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1234,19 +1246,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>430.8</t>
+    <t>415.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.3</t>
+    <t>4.2</t>
   </si>
   <si>
     <t>01일</t>
@@ -287,28 +287,49 @@
     <t>18일</t>
   </si>
   <si>
-    <t>511.7</t>
-  </si>
-  <si>
-    <t>7754.3</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>77.5</t>
+    <t>523.8</t>
+  </si>
+  <si>
+    <t>7766.4</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>77.7</t>
   </si>
   <si>
     <t>19일</t>
   </si>
   <si>
+    <t>366.5</t>
+  </si>
+  <si>
+    <t>8132.9</t>
+  </si>
+  <si>
+    <t>81.3</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
+    <t>179.1</t>
+  </si>
+  <si>
+    <t>8312.0</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>83.1</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>20일</t>
-  </si>
-  <si>
-    <t>21일</t>
   </si>
   <si>
     <t>22일</t>
@@ -1012,13 +1033,13 @@
         <v>96</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1026,19 +1047,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1046,19 +1067,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1066,19 +1087,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1086,19 +1107,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1106,19 +1127,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1126,19 +1147,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1146,19 +1167,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1166,19 +1187,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1186,19 +1207,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1206,19 +1227,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1226,19 +1247,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1246,19 +1267,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="120">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>415.6</t>
+    <t>401.7</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.2</t>
+    <t>4.0</t>
   </si>
   <si>
     <t>01일</t>
@@ -314,25 +314,37 @@
     <t>20일</t>
   </si>
   <si>
-    <t>179.1</t>
-  </si>
-  <si>
-    <t>8312.0</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>83.1</t>
+    <t>185.6</t>
+  </si>
+  <si>
+    <t>8318.5</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>83.2</t>
   </si>
   <si>
     <t>21일</t>
   </si>
   <si>
+    <t>117.0</t>
+  </si>
+  <si>
+    <t>8435.5</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>84.4</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>22일</t>
   </si>
   <si>
     <t>23일</t>
@@ -1073,13 +1085,13 @@
         <v>105</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1087,19 +1099,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1107,19 +1119,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1127,19 +1139,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1147,19 +1159,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1167,19 +1179,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1187,19 +1199,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1207,19 +1219,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1227,19 +1239,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1247,19 +1259,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1267,19 +1279,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>401.7</t>
+    <t>392.3</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>3.9</t>
   </si>
   <si>
     <t>01일</t>
@@ -164,9 +164,6 @@
     <t>4517.2</t>
   </si>
   <si>
-    <t>3.9</t>
-  </si>
-  <si>
     <t>45.2</t>
   </si>
   <si>
@@ -329,10 +326,10 @@
     <t>21일</t>
   </si>
   <si>
-    <t>117.0</t>
-  </si>
-  <si>
-    <t>8435.5</t>
+    <t>121.2</t>
+  </si>
+  <si>
+    <t>8439.7</t>
   </si>
   <si>
     <t>1.2</t>
@@ -344,10 +341,19 @@
     <t>22일</t>
   </si>
   <si>
+    <t>190.6</t>
+  </si>
+  <si>
+    <t>8630.3</t>
+  </si>
+  <si>
+    <t>86.3</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>23일</t>
   </si>
   <si>
     <t>24일</t>
@@ -848,10 +854,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -859,19 +865,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -879,19 +885,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
-      </c>
-      <c r="D13" t="s" s="32">
-        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>45</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -899,19 +905,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>61</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>62</v>
-      </c>
-      <c r="D14" t="s" s="37">
-        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
         <v>35</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -919,19 +925,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>65</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>66</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>67</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>68</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -939,19 +945,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>70</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>71</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>72</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>73</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -959,19 +965,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>75</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>76</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
         <v>77</v>
       </c>
-      <c r="E17" t="s" s="33">
+      <c r="F17" t="s" s="34">
         <v>78</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -979,19 +985,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>82</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>83</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -999,19 +1005,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>85</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>86</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>87</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>88</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1019,19 +1025,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>90</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>91</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>92</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>93</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1039,19 +1045,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>95</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>96</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
+        <v>67</v>
+      </c>
+      <c r="F21" t="s" s="34">
         <v>97</v>
-      </c>
-      <c r="E21" t="s" s="33">
-        <v>68</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1059,19 +1065,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>99</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>100</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>101</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>102</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1079,19 +1085,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>104</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>105</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>106</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>107</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1099,19 +1105,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>109</v>
-      </c>
-      <c r="C24" t="s" s="36">
-        <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
         <v>110</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1119,19 +1125,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1139,19 +1145,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1159,19 +1165,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1179,19 +1185,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1199,19 +1205,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1219,19 +1225,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1239,19 +1245,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1259,19 +1265,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1279,19 +1285,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
   <si>
     <t>No.</t>
   </si>
@@ -35,135 +35,138 @@
     <t>평균</t>
   </si>
   <si>
-    <t>392.3</t>
+    <t>397.5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>559.1</t>
+  </si>
+  <si>
+    <t>3108.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>530.7</t>
+  </si>
+  <si>
+    <t>3639.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>4122.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>4517.2</t>
+  </si>
+  <si>
     <t>3.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>552.2</t>
-  </si>
-  <si>
-    <t>1504.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>545.0</t>
-  </si>
-  <si>
-    <t>2049.1</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>500.1</t>
-  </si>
-  <si>
-    <t>2549.2</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>559.1</t>
-  </si>
-  <si>
-    <t>3108.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>31.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>530.7</t>
-  </si>
-  <si>
-    <t>3639.0</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>36.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>483.6</t>
-  </si>
-  <si>
-    <t>4122.6</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>41.2</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>4517.2</t>
-  </si>
-  <si>
     <t>45.2</t>
   </si>
   <si>
@@ -341,10 +344,10 @@
     <t>22일</t>
   </si>
   <si>
-    <t>190.6</t>
-  </si>
-  <si>
-    <t>8630.3</t>
+    <t>192.4</t>
+  </si>
+  <si>
+    <t>8632.1</t>
   </si>
   <si>
     <t>86.3</t>
@@ -353,10 +356,22 @@
     <t>23일</t>
   </si>
   <si>
+    <t>509.6</t>
+  </si>
+  <si>
+    <t>9141.7</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>91.4</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>24일</t>
   </si>
   <si>
     <t>25일</t>
@@ -854,10 +869,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -865,19 +880,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -885,19 +900,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>45</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -905,19 +920,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
         <v>35</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -925,19 +940,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -945,19 +960,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -965,19 +980,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -985,19 +1000,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1005,19 +1020,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1025,19 +1040,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1045,19 +1060,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1065,19 +1080,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1085,19 +1100,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1105,19 +1120,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1125,19 +1140,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1145,19 +1160,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1165,19 +1180,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1185,19 +1200,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1205,19 +1220,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1225,19 +1240,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1245,19 +1260,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1265,19 +1280,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1285,19 +1300,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>397.5</t>
+    <t>401.3</t>
   </si>
   <si>
     <t>-</t>
@@ -356,25 +356,31 @@
     <t>23일</t>
   </si>
   <si>
-    <t>509.6</t>
-  </si>
-  <si>
-    <t>9141.7</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>91.4</t>
+    <t>523.5</t>
+  </si>
+  <si>
+    <t>9155.6</t>
+  </si>
+  <si>
+    <t>91.6</t>
   </si>
   <si>
     <t>24일</t>
   </si>
   <si>
+    <t>475.0</t>
+  </si>
+  <si>
+    <t>9630.6</t>
+  </si>
+  <si>
+    <t>96.3</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>25일</t>
   </si>
   <si>
     <t>26일</t>
@@ -1149,10 +1155,10 @@
         <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
+        <v>93</v>
+      </c>
+      <c r="F25" t="s" s="34">
         <v>116</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>117</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1160,19 +1166,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>118</v>
-      </c>
-      <c r="C26" t="s" s="36">
-        <v>119</v>
       </c>
       <c r="D26" t="s" s="37">
         <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1180,19 +1186,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1200,19 +1206,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1220,19 +1226,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1240,19 +1246,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1260,19 +1266,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1280,19 +1286,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1300,19 +1306,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
   <si>
     <t>No.</t>
   </si>
@@ -368,22 +368,31 @@
     <t>24일</t>
   </si>
   <si>
-    <t>475.0</t>
-  </si>
-  <si>
-    <t>9630.6</t>
-  </si>
-  <si>
-    <t>96.3</t>
+    <t>482.7</t>
+  </si>
+  <si>
+    <t>9638.3</t>
+  </si>
+  <si>
+    <t>96.4</t>
   </si>
   <si>
     <t>25일</t>
   </si>
   <si>
+    <t>393.4</t>
+  </si>
+  <si>
+    <t>10031.7</t>
+  </si>
+  <si>
+    <t>100.3</t>
+  </si>
+  <si>
+    <t>26일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>26일</t>
   </si>
   <si>
     <t>27일</t>
@@ -1192,13 +1201,13 @@
         <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>122</v>
+        <v>50</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1206,19 +1215,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1226,19 +1235,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1246,19 +1255,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1266,19 +1275,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1286,19 +1295,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1306,19 +1315,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="140">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>401.3</t>
+    <t>397.1</t>
   </si>
   <si>
     <t>-</t>
@@ -380,25 +380,49 @@
     <t>25일</t>
   </si>
   <si>
-    <t>393.4</t>
-  </si>
-  <si>
-    <t>10031.7</t>
-  </si>
-  <si>
-    <t>100.3</t>
+    <t>400.1</t>
+  </si>
+  <si>
+    <t>10038.4</t>
+  </si>
+  <si>
+    <t>100.4</t>
   </si>
   <si>
     <t>26일</t>
   </si>
   <si>
+    <t>324.1</t>
+  </si>
+  <si>
+    <t>10362.5</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>103.6</t>
+  </si>
+  <si>
+    <t>27일</t>
+  </si>
+  <si>
+    <t>357.9</t>
+  </si>
+  <si>
+    <t>10720.4</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>107.2</t>
+  </si>
+  <si>
+    <t>28일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>27일</t>
-  </si>
-  <si>
-    <t>28일</t>
   </si>
   <si>
     <t>29일</t>
@@ -1204,7 +1228,7 @@
         <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s" s="34">
         <v>124</v>
@@ -1221,13 +1245,13 @@
         <v>126</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1235,19 +1259,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1255,19 +1279,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1275,19 +1299,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1295,19 +1319,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1315,19 +1339,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
   <si>
     <t>No.</t>
   </si>
@@ -35,357 +35,357 @@
     <t>평균</t>
   </si>
   <si>
-    <t>397.1</t>
+    <t>386.4</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>559.1</t>
+  </si>
+  <si>
+    <t>3108.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>530.7</t>
+  </si>
+  <si>
+    <t>3639.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>4122.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>4517.2</t>
+  </si>
+  <si>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>10일</t>
+  </si>
+  <si>
+    <t>460.2</t>
+  </si>
+  <si>
+    <t>4977.4</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>49.8</t>
+  </si>
+  <si>
+    <t>11일</t>
+  </si>
+  <si>
+    <t>480.9</t>
+  </si>
+  <si>
+    <t>5458.3</t>
+  </si>
+  <si>
+    <t>54.6</t>
+  </si>
+  <si>
+    <t>12일</t>
+  </si>
+  <si>
+    <t>559.0</t>
+  </si>
+  <si>
+    <t>6017.3</t>
+  </si>
+  <si>
+    <t>60.2</t>
+  </si>
+  <si>
+    <t>13일</t>
+  </si>
+  <si>
+    <t>368.3</t>
+  </si>
+  <si>
+    <t>6385.6</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>63.9</t>
+  </si>
+  <si>
+    <t>14일</t>
+  </si>
+  <si>
+    <t>337.8</t>
+  </si>
+  <si>
+    <t>6723.4</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>67.2</t>
+  </si>
+  <si>
+    <t>15일</t>
+  </si>
+  <si>
+    <t>210.0</t>
+  </si>
+  <si>
+    <t>6933.4</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>69.3</t>
+  </si>
+  <si>
+    <t>16일</t>
+  </si>
+  <si>
+    <t>148.3</t>
+  </si>
+  <si>
+    <t>7081.7</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>70.8</t>
+  </si>
+  <si>
+    <t>17일</t>
+  </si>
+  <si>
+    <t>160.9</t>
+  </si>
+  <si>
+    <t>7242.6</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>72.4</t>
+  </si>
+  <si>
+    <t>18일</t>
+  </si>
+  <si>
+    <t>523.8</t>
+  </si>
+  <si>
+    <t>7766.4</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>77.7</t>
+  </si>
+  <si>
+    <t>19일</t>
+  </si>
+  <si>
+    <t>366.5</t>
+  </si>
+  <si>
+    <t>8132.9</t>
+  </si>
+  <si>
+    <t>81.3</t>
+  </si>
+  <si>
+    <t>20일</t>
+  </si>
+  <si>
+    <t>185.6</t>
+  </si>
+  <si>
+    <t>8318.5</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>83.2</t>
+  </si>
+  <si>
+    <t>21일</t>
+  </si>
+  <si>
+    <t>121.2</t>
+  </si>
+  <si>
+    <t>8439.7</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>84.4</t>
+  </si>
+  <si>
+    <t>22일</t>
+  </si>
+  <si>
+    <t>192.4</t>
+  </si>
+  <si>
+    <t>8632.1</t>
+  </si>
+  <si>
+    <t>86.3</t>
+  </si>
+  <si>
+    <t>23일</t>
+  </si>
+  <si>
+    <t>523.5</t>
+  </si>
+  <si>
+    <t>9155.6</t>
+  </si>
+  <si>
+    <t>91.6</t>
+  </si>
+  <si>
+    <t>24일</t>
+  </si>
+  <si>
+    <t>482.7</t>
+  </si>
+  <si>
+    <t>9638.3</t>
+  </si>
+  <si>
+    <t>96.4</t>
+  </si>
+  <si>
+    <t>25일</t>
+  </si>
+  <si>
+    <t>400.1</t>
+  </si>
+  <si>
+    <t>10038.4</t>
+  </si>
+  <si>
     <t>4.0</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>552.2</t>
-  </si>
-  <si>
-    <t>1504.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>545.0</t>
-  </si>
-  <si>
-    <t>2049.1</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>500.1</t>
-  </si>
-  <si>
-    <t>2549.2</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>559.1</t>
-  </si>
-  <si>
-    <t>3108.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>31.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>530.7</t>
-  </si>
-  <si>
-    <t>3639.0</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>36.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>483.6</t>
-  </si>
-  <si>
-    <t>4122.6</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>41.2</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>4517.2</t>
-  </si>
-  <si>
-    <t>3.9</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>10일</t>
-  </si>
-  <si>
-    <t>460.2</t>
-  </si>
-  <si>
-    <t>4977.4</t>
-  </si>
-  <si>
-    <t>4.6</t>
-  </si>
-  <si>
-    <t>49.8</t>
-  </si>
-  <si>
-    <t>11일</t>
-  </si>
-  <si>
-    <t>480.9</t>
-  </si>
-  <si>
-    <t>5458.3</t>
-  </si>
-  <si>
-    <t>54.6</t>
-  </si>
-  <si>
-    <t>12일</t>
-  </si>
-  <si>
-    <t>559.0</t>
-  </si>
-  <si>
-    <t>6017.3</t>
-  </si>
-  <si>
-    <t>60.2</t>
-  </si>
-  <si>
-    <t>13일</t>
-  </si>
-  <si>
-    <t>368.3</t>
-  </si>
-  <si>
-    <t>6385.6</t>
-  </si>
-  <si>
-    <t>3.7</t>
-  </si>
-  <si>
-    <t>63.9</t>
-  </si>
-  <si>
-    <t>14일</t>
-  </si>
-  <si>
-    <t>337.8</t>
-  </si>
-  <si>
-    <t>6723.4</t>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
-    <t>67.2</t>
-  </si>
-  <si>
-    <t>15일</t>
-  </si>
-  <si>
-    <t>210.0</t>
-  </si>
-  <si>
-    <t>6933.4</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>69.3</t>
-  </si>
-  <si>
-    <t>16일</t>
-  </si>
-  <si>
-    <t>148.3</t>
-  </si>
-  <si>
-    <t>7081.7</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>70.8</t>
-  </si>
-  <si>
-    <t>17일</t>
-  </si>
-  <si>
-    <t>160.9</t>
-  </si>
-  <si>
-    <t>7242.6</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>72.4</t>
-  </si>
-  <si>
-    <t>18일</t>
-  </si>
-  <si>
-    <t>523.8</t>
-  </si>
-  <si>
-    <t>7766.4</t>
-  </si>
-  <si>
-    <t>5.2</t>
-  </si>
-  <si>
-    <t>77.7</t>
-  </si>
-  <si>
-    <t>19일</t>
-  </si>
-  <si>
-    <t>366.5</t>
-  </si>
-  <si>
-    <t>8132.9</t>
-  </si>
-  <si>
-    <t>81.3</t>
-  </si>
-  <si>
-    <t>20일</t>
-  </si>
-  <si>
-    <t>185.6</t>
-  </si>
-  <si>
-    <t>8318.5</t>
-  </si>
-  <si>
-    <t>1.9</t>
-  </si>
-  <si>
-    <t>83.2</t>
-  </si>
-  <si>
-    <t>21일</t>
-  </si>
-  <si>
-    <t>121.2</t>
-  </si>
-  <si>
-    <t>8439.7</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>84.4</t>
-  </si>
-  <si>
-    <t>22일</t>
-  </si>
-  <si>
-    <t>192.4</t>
-  </si>
-  <si>
-    <t>8632.1</t>
-  </si>
-  <si>
-    <t>86.3</t>
-  </si>
-  <si>
-    <t>23일</t>
-  </si>
-  <si>
-    <t>523.5</t>
-  </si>
-  <si>
-    <t>9155.6</t>
-  </si>
-  <si>
-    <t>91.6</t>
-  </si>
-  <si>
-    <t>24일</t>
-  </si>
-  <si>
-    <t>482.7</t>
-  </si>
-  <si>
-    <t>9638.3</t>
-  </si>
-  <si>
-    <t>96.4</t>
-  </si>
-  <si>
-    <t>25일</t>
-  </si>
-  <si>
-    <t>400.1</t>
-  </si>
-  <si>
-    <t>10038.4</t>
-  </si>
-  <si>
     <t>100.4</t>
   </si>
   <si>
@@ -422,10 +422,22 @@
     <t>28일</t>
   </si>
   <si>
+    <t>97.6</t>
+  </si>
+  <si>
+    <t>10818.0</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>108.2</t>
+  </si>
+  <si>
+    <t>29일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>29일</t>
   </si>
   <si>
     <t>30일</t>
@@ -908,10 +920,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s" s="34">
         <v>50</v>
-      </c>
-      <c r="F11" t="s" s="34">
-        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -919,19 +931,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s" s="36">
         <v>52</v>
       </c>
-      <c r="C12" t="s" s="36">
+      <c r="D12" t="s" s="37">
         <v>53</v>
       </c>
-      <c r="D12" t="s" s="37">
+      <c r="E12" t="s" s="38">
         <v>54</v>
       </c>
-      <c r="E12" t="s" s="38">
+      <c r="F12" t="s" s="39">
         <v>55</v>
-      </c>
-      <c r="F12" t="s" s="39">
-        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -939,19 +951,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s" s="31">
         <v>57</v>
       </c>
-      <c r="C13" t="s" s="31">
+      <c r="D13" t="s" s="32">
         <v>58</v>
-      </c>
-      <c r="D13" t="s" s="32">
-        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>45</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -959,19 +971,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s" s="36">
         <v>61</v>
       </c>
-      <c r="C14" t="s" s="36">
+      <c r="D14" t="s" s="37">
         <v>62</v>
-      </c>
-      <c r="D14" t="s" s="37">
-        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
         <v>35</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -979,19 +991,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s" s="31">
         <v>65</v>
       </c>
-      <c r="C15" t="s" s="31">
+      <c r="D15" t="s" s="32">
         <v>66</v>
       </c>
-      <c r="D15" t="s" s="32">
+      <c r="E15" t="s" s="33">
         <v>67</v>
       </c>
-      <c r="E15" t="s" s="33">
+      <c r="F15" t="s" s="34">
         <v>68</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -999,19 +1011,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>70</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>71</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>72</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>73</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1019,19 +1031,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>75</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>76</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
         <v>77</v>
       </c>
-      <c r="E17" t="s" s="33">
+      <c r="F17" t="s" s="34">
         <v>78</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1039,19 +1051,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>82</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>83</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1059,19 +1071,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>85</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>86</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>87</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>88</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1079,19 +1091,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>90</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>91</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>92</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>93</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1099,19 +1111,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>95</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>96</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
+        <v>67</v>
+      </c>
+      <c r="F21" t="s" s="34">
         <v>97</v>
-      </c>
-      <c r="E21" t="s" s="33">
-        <v>68</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1119,19 +1131,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>99</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>100</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>101</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>102</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1139,19 +1151,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>104</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>105</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>106</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>107</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1159,19 +1171,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>109</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>110</v>
       </c>
-      <c r="D24" t="s" s="37">
+      <c r="E24" t="s" s="38">
+        <v>101</v>
+      </c>
+      <c r="F24" t="s" s="39">
         <v>111</v>
-      </c>
-      <c r="E24" t="s" s="38">
-        <v>102</v>
-      </c>
-      <c r="F24" t="s" s="39">
-        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1179,19 +1191,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>113</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>114</v>
       </c>
-      <c r="D25" t="s" s="32">
+      <c r="E25" t="s" s="33">
+        <v>92</v>
+      </c>
+      <c r="F25" t="s" s="34">
         <v>115</v>
-      </c>
-      <c r="E25" t="s" s="33">
-        <v>93</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1199,19 +1211,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>116</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>117</v>
       </c>
-      <c r="C26" t="s" s="36">
+      <c r="D26" t="s" s="37">
         <v>118</v>
-      </c>
-      <c r="D26" t="s" s="37">
-        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>45</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1219,16 +1231,16 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>121</v>
       </c>
-      <c r="C27" t="s" s="31">
+      <c r="D27" t="s" s="32">
         <v>122</v>
       </c>
-      <c r="D27" t="s" s="32">
+      <c r="E27" t="s" s="33">
         <v>123</v>
-      </c>
-      <c r="E27" t="s" s="33">
-        <v>9</v>
       </c>
       <c r="F27" t="s" s="34">
         <v>124</v>
@@ -1285,13 +1297,13 @@
         <v>136</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1299,19 +1311,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1319,19 +1331,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1339,19 +1351,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="149">
   <si>
     <t>No.</t>
   </si>
@@ -35,135 +35,138 @@
     <t>평균</t>
   </si>
   <si>
-    <t>386.4</t>
+    <t>383.6</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>01일</t>
+  </si>
+  <si>
+    <t>465.5</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>02일</t>
+  </si>
+  <si>
+    <t>486.4</t>
+  </si>
+  <si>
+    <t>951.9</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>03일</t>
+  </si>
+  <si>
+    <t>552.2</t>
+  </si>
+  <si>
+    <t>1504.1</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>04일</t>
+  </si>
+  <si>
+    <t>545.0</t>
+  </si>
+  <si>
+    <t>2049.1</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>05일</t>
+  </si>
+  <si>
+    <t>500.1</t>
+  </si>
+  <si>
+    <t>2549.2</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>25.5</t>
+  </si>
+  <si>
+    <t>06일</t>
+  </si>
+  <si>
+    <t>559.1</t>
+  </si>
+  <si>
+    <t>3108.3</t>
+  </si>
+  <si>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>07일</t>
+  </si>
+  <si>
+    <t>530.7</t>
+  </si>
+  <si>
+    <t>3639.0</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>08일</t>
+  </si>
+  <si>
+    <t>483.6</t>
+  </si>
+  <si>
+    <t>4122.6</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>41.2</t>
+  </si>
+  <si>
+    <t>09일</t>
+  </si>
+  <si>
+    <t>394.6</t>
+  </si>
+  <si>
+    <t>4517.2</t>
+  </si>
+  <si>
     <t>3.9</t>
   </si>
   <si>
-    <t>01일</t>
-  </si>
-  <si>
-    <t>465.5</t>
-  </si>
-  <si>
-    <t>4.7</t>
-  </si>
-  <si>
-    <t>02일</t>
-  </si>
-  <si>
-    <t>486.4</t>
-  </si>
-  <si>
-    <t>951.9</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>9.5</t>
-  </si>
-  <si>
-    <t>03일</t>
-  </si>
-  <si>
-    <t>552.2</t>
-  </si>
-  <si>
-    <t>1504.1</t>
-  </si>
-  <si>
-    <t>5.5</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>04일</t>
-  </si>
-  <si>
-    <t>545.0</t>
-  </si>
-  <si>
-    <t>2049.1</t>
-  </si>
-  <si>
-    <t>20.5</t>
-  </si>
-  <si>
-    <t>05일</t>
-  </si>
-  <si>
-    <t>500.1</t>
-  </si>
-  <si>
-    <t>2549.2</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>25.5</t>
-  </si>
-  <si>
-    <t>06일</t>
-  </si>
-  <si>
-    <t>559.1</t>
-  </si>
-  <si>
-    <t>3108.3</t>
-  </si>
-  <si>
-    <t>5.6</t>
-  </si>
-  <si>
-    <t>31.1</t>
-  </si>
-  <si>
-    <t>07일</t>
-  </si>
-  <si>
-    <t>530.7</t>
-  </si>
-  <si>
-    <t>3639.0</t>
-  </si>
-  <si>
-    <t>5.3</t>
-  </si>
-  <si>
-    <t>36.4</t>
-  </si>
-  <si>
-    <t>08일</t>
-  </si>
-  <si>
-    <t>483.6</t>
-  </si>
-  <si>
-    <t>4122.6</t>
-  </si>
-  <si>
-    <t>4.8</t>
-  </si>
-  <si>
-    <t>41.2</t>
-  </si>
-  <si>
-    <t>09일</t>
-  </si>
-  <si>
-    <t>394.6</t>
-  </si>
-  <si>
-    <t>4517.2</t>
-  </si>
-  <si>
     <t>45.2</t>
   </si>
   <si>
@@ -437,10 +440,22 @@
     <t>29일</t>
   </si>
   <si>
+    <t>306.1</t>
+  </si>
+  <si>
+    <t>11124.1</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>111.2</t>
+  </si>
+  <si>
+    <t>30일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>30일</t>
   </si>
   <si>
     <t>31일</t>
@@ -920,10 +935,10 @@
         <v>49</v>
       </c>
       <c r="E11" t="s" s="33">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="F11" t="s" s="34">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="17.25" customHeight="1">
@@ -931,19 +946,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s" s="35">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s" s="37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s" s="38">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s" s="39">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" ht="17.25" customHeight="1">
@@ -951,19 +966,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s" s="30">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s" s="31">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="32">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s" s="33">
         <v>45</v>
       </c>
       <c r="F13" t="s" s="34">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1">
@@ -971,19 +986,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s" s="35">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s" s="36">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="37">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s" s="38">
         <v>35</v>
       </c>
       <c r="F14" t="s" s="39">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1">
@@ -991,19 +1006,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="30">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s" s="31">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s" s="32">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s" s="34">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1011,19 +1026,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s" s="36">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s" s="37">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s" s="38">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s" s="39">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1031,19 +1046,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s" s="31">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s" s="32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" t="s" s="33">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" t="s" s="34">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1051,19 +1066,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s" s="36">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s" s="37">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s" s="38">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" t="s" s="39">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1071,19 +1086,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s" s="31">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s" s="32">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s" s="33">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s" s="34">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1091,19 +1106,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s" s="36">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s" s="37">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s" s="38">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s" s="39">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1111,19 +1126,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s" s="31">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s" s="32">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s" s="33">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s" s="34">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1131,19 +1146,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s" s="36">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s" s="37">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s" s="38">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s" s="39">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1151,19 +1166,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s" s="31">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s" s="32">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s" s="33">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s" s="34">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1171,19 +1186,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s" s="36">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s" s="37">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s" s="38">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s" s="39">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1191,19 +1206,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s" s="31">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s" s="32">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E25" t="s" s="33">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" t="s" s="34">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1211,19 +1226,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s" s="36">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s" s="37">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>45</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1231,19 +1246,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C27" t="s" s="31">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s" s="32">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s" s="33">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F27" t="s" s="34">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1251,19 +1266,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s" s="36">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s" s="37">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s" s="38">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F28" t="s" s="39">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1271,19 +1286,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s" s="31">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s" s="32">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s" s="33">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s" s="34">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1291,19 +1306,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s" s="36">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s" s="37">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s" s="38">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s" s="39">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1311,19 +1326,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s" s="31">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s" s="32">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E31" t="s" s="33">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s" s="34">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1331,19 +1346,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s" s="36">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1351,19 +1366,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="153">
   <si>
     <t>No.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>평균</t>
   </si>
   <si>
-    <t>383.6</t>
+    <t>379.0</t>
   </si>
   <si>
     <t>-</t>
@@ -455,10 +455,22 @@
     <t>30일</t>
   </si>
   <si>
+    <t>244.4</t>
+  </si>
+  <si>
+    <t>11368.5</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>113.7</t>
+  </si>
+  <si>
+    <t>31일</t>
+  </si>
+  <si>
     <t>0.0</t>
-  </si>
-  <si>
-    <t>31일</t>
   </si>
 </sst>
 </file>
@@ -1352,13 +1364,13 @@
         <v>147</v>
       </c>
       <c r="D32" t="s" s="37">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E32" t="s" s="38">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F32" t="s" s="39">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1366,19 +1378,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s" s="31">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D33" t="s" s="32">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/past_data/site_8024/2026-08-01.xlsx
+++ b/past_data/site_8024/2026-08-01.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="155">
   <si>
     <t>No.</t>
   </si>
@@ -35,13 +35,13 @@
     <t>평균</t>
   </si>
   <si>
-    <t>379.0</t>
+    <t>369.0</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>3.8</t>
+    <t>3.7</t>
   </si>
   <si>
     <t>01일</t>
@@ -218,9 +218,6 @@
     <t>6385.6</t>
   </si>
   <si>
-    <t>3.7</t>
-  </si>
-  <si>
     <t>63.9</t>
   </si>
   <si>
@@ -470,7 +467,16 @@
     <t>31일</t>
   </si>
   <si>
-    <t>0.0</t>
+    <t>71.9</t>
+  </si>
+  <si>
+    <t>11440.4</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>114.4</t>
   </si>
 </sst>
 </file>
@@ -1027,10 +1033,10 @@
         <v>67</v>
       </c>
       <c r="E15" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s" s="34">
         <v>68</v>
-      </c>
-      <c r="F15" t="s" s="34">
-        <v>69</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1">
@@ -1038,19 +1044,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s" s="35">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s" s="36">
         <v>70</v>
       </c>
-      <c r="C16" t="s" s="36">
+      <c r="D16" t="s" s="37">
         <v>71</v>
       </c>
-      <c r="D16" t="s" s="37">
+      <c r="E16" t="s" s="38">
         <v>72</v>
       </c>
-      <c r="E16" t="s" s="38">
+      <c r="F16" t="s" s="39">
         <v>73</v>
-      </c>
-      <c r="F16" t="s" s="39">
-        <v>74</v>
       </c>
     </row>
     <row r="17" ht="17.25" customHeight="1">
@@ -1058,19 +1064,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s" s="30">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s" s="31">
         <v>75</v>
       </c>
-      <c r="C17" t="s" s="31">
+      <c r="D17" t="s" s="32">
         <v>76</v>
       </c>
-      <c r="D17" t="s" s="32">
+      <c r="E17" t="s" s="33">
         <v>77</v>
       </c>
-      <c r="E17" t="s" s="33">
+      <c r="F17" t="s" s="34">
         <v>78</v>
-      </c>
-      <c r="F17" t="s" s="34">
-        <v>79</v>
       </c>
     </row>
     <row r="18" ht="17.25" customHeight="1">
@@ -1078,19 +1084,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s" s="36">
         <v>80</v>
       </c>
-      <c r="C18" t="s" s="36">
+      <c r="D18" t="s" s="37">
         <v>81</v>
       </c>
-      <c r="D18" t="s" s="37">
+      <c r="E18" t="s" s="38">
         <v>82</v>
       </c>
-      <c r="E18" t="s" s="38">
+      <c r="F18" t="s" s="39">
         <v>83</v>
-      </c>
-      <c r="F18" t="s" s="39">
-        <v>84</v>
       </c>
     </row>
     <row r="19" ht="17.25" customHeight="1">
@@ -1098,19 +1104,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s" s="30">
+        <v>84</v>
+      </c>
+      <c r="C19" t="s" s="31">
         <v>85</v>
       </c>
-      <c r="C19" t="s" s="31">
+      <c r="D19" t="s" s="32">
         <v>86</v>
       </c>
-      <c r="D19" t="s" s="32">
+      <c r="E19" t="s" s="33">
         <v>87</v>
       </c>
-      <c r="E19" t="s" s="33">
+      <c r="F19" t="s" s="34">
         <v>88</v>
-      </c>
-      <c r="F19" t="s" s="34">
-        <v>89</v>
       </c>
     </row>
     <row r="20" ht="17.25" customHeight="1">
@@ -1118,19 +1124,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="35">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s" s="36">
         <v>90</v>
       </c>
-      <c r="C20" t="s" s="36">
+      <c r="D20" t="s" s="37">
         <v>91</v>
       </c>
-      <c r="D20" t="s" s="37">
+      <c r="E20" t="s" s="38">
         <v>92</v>
       </c>
-      <c r="E20" t="s" s="38">
+      <c r="F20" t="s" s="39">
         <v>93</v>
-      </c>
-      <c r="F20" t="s" s="39">
-        <v>94</v>
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1">
@@ -1138,19 +1144,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="30">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s" s="31">
         <v>95</v>
       </c>
-      <c r="C21" t="s" s="31">
+      <c r="D21" t="s" s="32">
         <v>96</v>
       </c>
-      <c r="D21" t="s" s="32">
+      <c r="E21" t="s" s="33">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s" s="34">
         <v>97</v>
-      </c>
-      <c r="E21" t="s" s="33">
-        <v>68</v>
-      </c>
-      <c r="F21" t="s" s="34">
-        <v>98</v>
       </c>
     </row>
     <row r="22" ht="17.25" customHeight="1">
@@ -1158,19 +1164,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="35">
+        <v>98</v>
+      </c>
+      <c r="C22" t="s" s="36">
         <v>99</v>
       </c>
-      <c r="C22" t="s" s="36">
+      <c r="D22" t="s" s="37">
         <v>100</v>
       </c>
-      <c r="D22" t="s" s="37">
+      <c r="E22" t="s" s="38">
         <v>101</v>
       </c>
-      <c r="E22" t="s" s="38">
+      <c r="F22" t="s" s="39">
         <v>102</v>
-      </c>
-      <c r="F22" t="s" s="39">
-        <v>103</v>
       </c>
     </row>
     <row r="23" ht="17.25" customHeight="1">
@@ -1178,19 +1184,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="30">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s" s="31">
         <v>104</v>
       </c>
-      <c r="C23" t="s" s="31">
+      <c r="D23" t="s" s="32">
         <v>105</v>
       </c>
-      <c r="D23" t="s" s="32">
+      <c r="E23" t="s" s="33">
         <v>106</v>
       </c>
-      <c r="E23" t="s" s="33">
+      <c r="F23" t="s" s="34">
         <v>107</v>
-      </c>
-      <c r="F23" t="s" s="34">
-        <v>108</v>
       </c>
     </row>
     <row r="24" ht="17.25" customHeight="1">
@@ -1198,19 +1204,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="35">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s" s="36">
         <v>109</v>
       </c>
-      <c r="C24" t="s" s="36">
+      <c r="D24" t="s" s="37">
         <v>110</v>
       </c>
-      <c r="D24" t="s" s="37">
+      <c r="E24" t="s" s="38">
+        <v>101</v>
+      </c>
+      <c r="F24" t="s" s="39">
         <v>111</v>
-      </c>
-      <c r="E24" t="s" s="38">
-        <v>102</v>
-      </c>
-      <c r="F24" t="s" s="39">
-        <v>112</v>
       </c>
     </row>
     <row r="25" ht="17.25" customHeight="1">
@@ -1218,19 +1224,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="30">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s" s="31">
         <v>113</v>
       </c>
-      <c r="C25" t="s" s="31">
+      <c r="D25" t="s" s="32">
         <v>114</v>
       </c>
-      <c r="D25" t="s" s="32">
+      <c r="E25" t="s" s="33">
+        <v>92</v>
+      </c>
+      <c r="F25" t="s" s="34">
         <v>115</v>
-      </c>
-      <c r="E25" t="s" s="33">
-        <v>93</v>
-      </c>
-      <c r="F25" t="s" s="34">
-        <v>116</v>
       </c>
     </row>
     <row r="26" ht="17.25" customHeight="1">
@@ -1238,19 +1244,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="35">
+        <v>116</v>
+      </c>
+      <c r="C26" t="s" s="36">
         <v>117</v>
       </c>
-      <c r="C26" t="s" s="36">
+      <c r="D26" t="s" s="37">
         <v>118</v>
-      </c>
-      <c r="D26" t="s" s="37">
-        <v>119</v>
       </c>
       <c r="E26" t="s" s="38">
         <v>45</v>
       </c>
       <c r="F26" t="s" s="39">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" ht="17.25" customHeight="1">
@@ -1258,19 +1264,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="30">
+        <v>120</v>
+      </c>
+      <c r="C27" t="s" s="31">
         <v>121</v>
       </c>
-      <c r="C27" t="s" s="31">
+      <c r="D27" t="s" s="32">
         <v>122</v>
       </c>
-      <c r="D27" t="s" s="32">
+      <c r="E27" t="s" s="33">
         <v>123</v>
       </c>
-      <c r="E27" t="s" s="33">
+      <c r="F27" t="s" s="34">
         <v>124</v>
-      </c>
-      <c r="F27" t="s" s="34">
-        <v>125</v>
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
@@ -1278,19 +1284,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="35">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s" s="36">
         <v>126</v>
       </c>
-      <c r="C28" t="s" s="36">
+      <c r="D28" t="s" s="37">
         <v>127</v>
       </c>
-      <c r="D28" t="s" s="37">
+      <c r="E28" t="s" s="38">
         <v>128</v>
       </c>
-      <c r="E28" t="s" s="38">
+      <c r="F28" t="s" s="39">
         <v>129</v>
-      </c>
-      <c r="F28" t="s" s="39">
-        <v>130</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
@@ -1298,19 +1304,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="30">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s" s="31">
         <v>131</v>
       </c>
-      <c r="C29" t="s" s="31">
+      <c r="D29" t="s" s="32">
         <v>132</v>
       </c>
-      <c r="D29" t="s" s="32">
+      <c r="E29" t="s" s="33">
         <v>133</v>
       </c>
-      <c r="E29" t="s" s="33">
+      <c r="F29" t="s" s="34">
         <v>134</v>
-      </c>
-      <c r="F29" t="s" s="34">
-        <v>135</v>
       </c>
     </row>
     <row r="30" ht="17.25" customHeight="1">
@@ -1318,19 +1324,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="35">
+        <v>135</v>
+      </c>
+      <c r="C30" t="s" s="36">
         <v>136</v>
       </c>
-      <c r="C30" t="s" s="36">
+      <c r="D30" t="s" s="37">
         <v>137</v>
       </c>
-      <c r="D30" t="s" s="37">
+      <c r="E30" t="s" s="38">
         <v>138</v>
       </c>
-      <c r="E30" t="s" s="38">
+      <c r="F30" t="s" s="39">
         <v>139</v>
-      </c>
-      <c r="F30" t="s" s="39">
-        <v>140</v>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1">
@@ -1338,19 +1344,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="30">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s" s="31">
         <v>141</v>
       </c>
-      <c r="C31" t="s" s="31">
+      <c r="D31" t="s" s="32">
         <v>142</v>
       </c>
-      <c r="D31" t="s" s="32">
+      <c r="E31" t="s" s="33">
         <v>143</v>
       </c>
-      <c r="E31" t="s" s="33">
+      <c r="F31" t="s" s="34">
         <v>144</v>
-      </c>
-      <c r="F31" t="s" s="34">
-        <v>145</v>
       </c>
     </row>
     <row r="32" ht="17.25" customHeight="1">
@@ -1358,19 +1364,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="35">
+        <v>145</v>
+      </c>
+      <c r="C32" t="s" s="36">
         <v>146</v>
       </c>
-      <c r="C32" t="s" s="36">
+      <c r="D32" t="s" s="37">
         <v>147</v>
       </c>
-      <c r="D32" t="s" s="37">
+      <c r="E32" t="s" s="38">
         <v>148</v>
       </c>
-      <c r="E32" t="s" s="38">
+      <c r="F32" t="s" s="39">
         <v>149</v>
-      </c>
-      <c r="F32" t="s" s="39">
-        <v>150</v>
       </c>
     </row>
     <row r="33" ht="17.25" customHeight="1">
@@ -1378,19 +1384,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="30">
+        <v>150</v>
+      </c>
+      <c r="C33" t="s" s="31">
         <v>151</v>
-      </c>
-      <c r="C33" t="s" s="31">
-        <v>152</v>
       </c>
       <c r="D33" t="s" s="32">
         <v>152</v>
       </c>
       <c r="E33" t="s" s="33">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F33" t="s" s="34">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
